--- a/temp/csv_to_excel/file.xlsx
+++ b/temp/csv_to_excel/file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ЕА000505354</t>
+          <t>ЕА000510007</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23.11.2025</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -517,25 +517,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Д7-00000438</t>
+          <t>00-00000440</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Батон Крымский новый</t>
+          <t>Батон Бутербродный, нарезка</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -545,22 +545,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>39,091</t>
+          <t>44,545</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1 172,73</t>
+          <t>178,18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1 290</t>
+          <t>196</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>117,27</t>
+          <t>17,82</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -568,53 +568,767 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>С0000000473</t>
+          <t>3M-00130396</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Хлеб Бездрожжевой формовой</t>
+          <t>Батон Горчичный, нарезка</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>25,453</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>76,36</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,64</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>РМ-00470030</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>44,5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Батон Горчичный, нарезка</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>0,4</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>47,273</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>567,27</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>56,73</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>40,455</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>161,82</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16,18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>РМ-00003548</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Батон Карельский, нарезка</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Д7-00000438</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Батон Крымский новый</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0,45</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>39,091</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>390,91</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>39,09</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00-00000439</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>47,5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Батон Крымский новый, нарезка</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0,45</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>43,181</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>302,27</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>332,5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>30,23</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>РМ-00467553</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Пирожок с абрикосовым конфитюром, упаковка</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>29,09</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>87,27</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,73</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>РМ-00461560</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Пирожок с вишенкой, упаковка</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>РМ-00467552</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Пирожок с малиновым конфитюром, упаковка</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>РМ-00461559</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Пирожок с яблочком, упаковка</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>27,273</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>81,82</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8,18</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>С0000013583</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Плюшка сдобная</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>33,636</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>168,18</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>16,82</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>СЭСЭ0023145</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Рогалик Одесский</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>РМ-00468401</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Хлеб Бездрожжевой формовой, нарезка</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>48,182</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>289,09</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>28,91</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>РМ-00457077</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Хлеб с отрубями подовый, нарезка</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>49,09</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>98,18</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>9,82</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>РМ-00469494</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Хлеб Семейный подовый, нарезка</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>РМ-00463673</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Хлеб Семейный подовый, нарезка</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0,6</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/temp/csv_to_excel/file.xlsx
+++ b/temp/csv_to_excel/file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ЕА000510007</t>
+          <t>ЕА000572752</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -823,25 +823,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>РМ-00467553</t>
+          <t>РМ-00468830</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Пирожок с абрикосовым конфитюром, упаковка</t>
+          <t>Булочка Фаст-фуд, упаковка (3шт*0,080)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -851,22 +851,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>29,09</t>
+          <t>61,82</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>87,27</t>
+          <t>123,64</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8,73</t>
+          <t>12,36</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -907,17 +907,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -925,7 +925,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>РМ-00467552</t>
+          <t>РМ-00467572</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -933,12 +933,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Пирожок с малиновым конфитюром, упаковка</t>
+          <t>Пирожок с картошкой, упаковка</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27,273</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>81,82</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8,18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -976,7 +976,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>РМ-00461559</t>
+          <t>РМ-00467551</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -984,12 +984,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Пирожок с яблочком, упаковка</t>
+          <t>Пирожок с маковой начинкой, упаковка</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1004,22 +1004,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>27,273</t>
+          <t>29,09</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>81,82</t>
+          <t>87,27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8,18</t>
+          <t>8,73</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1027,25 +1027,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>С0000013583</t>
+          <t>РМ-00467552</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Плюшка сдобная</t>
+          <t>Пирожок с малиновым конфитюром, упаковка</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1055,22 +1055,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>33,636</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>168,18</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16,82</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1078,25 +1078,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>СЭСЭ0023145</t>
+          <t>РМ-00461559</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Рогалик Одесский</t>
+          <t>Пирожок с яблочком, упаковка</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1106,22 +1106,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27,273</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>81,82</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8,18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1129,25 +1129,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>РМ-00468401</t>
+          <t>С0000013583</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Хлеб Бездрожжевой формовой, нарезка</t>
+          <t>Плюшка сдобная</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1157,22 +1157,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>48,182</t>
+          <t>33,636</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>289,09</t>
+          <t>168,18</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>185</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28,91</t>
+          <t>16,82</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1180,25 +1180,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>РМ-00457077</t>
+          <t>СЭСЭ0023145</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Хлеб с отрубями подовый, нарезка</t>
+          <t>Рогалик Одесский</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1208,22 +1208,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>49,09</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>98,18</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>165</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1231,25 +1231,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>РМ-00469494</t>
+          <t>РМ-00468401</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Хлеб Семейный подовый, нарезка</t>
+          <t>Хлеб Бездрожжевой формовой, нарезка</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1259,22 +1259,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48,182</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>289,09</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>318</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28,91</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1282,53 +1282,257 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>РМ-00457077</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Хлеб с отрубями подовый, нарезка</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>49,09</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>147,27</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>14,73</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>РМ-00469494</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Хлеб Семейный подовый, нарезка</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>РМ-00463673</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B20" t="n">
         <v>7</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Хлеб Семейный подовый, нарезка</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>0,6</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>РМ-00467556</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Хлеб Тостерный формовой, нарезка</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>44,55</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>44,55</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4,45</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>С0000013579</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Хлеб Тостерный формовой, нарезка</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0,6</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>74,55</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>74,55</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>7,45</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
